--- a/check_in_forms/018_office_check_in_form--check_in_forms.xlsx
+++ b/check_in_forms/018_office_check_in_form--check_in_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1125,8 +1125,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'johndoe'}</t>
+          <t>johndoe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'johndoe'}</t>
+          <t>johndoe</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'janedoe'}</t>
+          <t>janedoe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'janedoe'}</t>
+          <t>janedoe</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'google_forms'}</t>
+          <t>google_forms</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'google_forms'}</t>
+          <t>google forms</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'google_sheets'}</t>
+          <t>google_sheets</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'google_sheets'}</t>
+          <t>google sheets</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'jupyter'}</t>
+          <t>jupyter</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'jupyter'}</t>
+          <t>jupyter</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'checked_in'}</t>
+          <t>checked_in</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'checked in'}</t>
+          <t>checked in</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'checked_out'}</t>
+          <t>checked_out</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'checked out'}</t>
+          <t>checked out</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'unknown'}</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'unknown'}</t>
+          <t>unknown</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'user1'}</t>
+          <t>user1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'user1'}</t>
+          <t>user1</t>
         </is>
       </c>
     </row>
@@ -1324,12 +1324,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'user2'}</t>
+          <t>user2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': 'user2'}</t>
+          <t>user2</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_'user3'}</t>
+          <t>user3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': 'user3'}</t>
+          <t>user3</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'name':_'desktop'}</t>
+          <t>desktop</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'name': 'desktop'}</t>
+          <t>desktop</t>
         </is>
       </c>
     </row>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'name':_'mobile'}</t>
+          <t>mobile</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'name': 'mobile'}</t>
+          <t>mobile</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'name':_'once'}</t>
+          <t>once</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'name': 'once'}</t>
+          <t>once</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'name':_'multiple'}</t>
+          <t>multiple</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'name': 'multiple'}</t>
+          <t>multiple</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'name':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'name': 'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
     </row>
@@ -1443,12 +1443,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'name':_'checkin'}</t>
+          <t>checkin</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'name': 'checkin'}</t>
+          <t>checkin</t>
         </is>
       </c>
     </row>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'name':_'visit'}</t>
+          <t>visit</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'name': 'visit'}</t>
+          <t>visit</t>
         </is>
       </c>
     </row>
@@ -1477,12 +1477,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'name':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'name': 'active'}</t>
+          <t>active</t>
         </is>
       </c>
     </row>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'name':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'name': 'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
     </row>
